--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-08.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-08.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
           <t>PnL_R$</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro_Green_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -538,37 +543,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ESTONIA 1</t>
+          <t>SOUTH KOREA 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Trans Narva x Tallinna FC Flora</t>
+          <t>Incheon Utd x Bucheon FC 1995</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>Incheon Utd</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Bucheon FC 1995</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -577,43 +582,42 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="K2" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>18.52</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.95</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>17.59</v>
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="3">
@@ -624,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -634,27 +638,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nomme Kalju x Nomme Utd</t>
+          <t>Trans Narva x Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -663,20 +667,20 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K3" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="L3" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -699,8 +703,9 @@
         <v>0.95</v>
       </c>
       <c r="T3" t="n">
-        <v>18.27</v>
-      </c>
+        <v>17.59</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -710,27 +715,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>ESTONIA 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bournemouth x Lincoln</t>
+          <t>Nomme Kalju x Nomme Utd</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -749,20 +754,20 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="K4" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="L4" t="n">
-        <v>17.86</v>
+        <v>19.23</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -785,8 +790,9 @@
         <v>0.95</v>
       </c>
       <c r="T4" t="n">
-        <v>16.97</v>
-      </c>
+        <v>18.27</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -796,7 +802,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -806,27 +812,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Millwall x Newcastle</t>
+          <t>Bournemouth x Lincoln</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -835,20 +841,20 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="K5" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="L5" t="n">
-        <v>15.62</v>
+        <v>17.86</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -871,8 +877,9 @@
         <v>0.95</v>
       </c>
       <c r="T5" t="n">
-        <v>14.84</v>
-      </c>
+        <v>16.97</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -882,37 +889,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Criciuma x Juventude</t>
+          <t>Millwall x Newcastle</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Over 4.5 FT</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -921,20 +928,20 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="K6" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="L6" t="n">
-        <v>5.26</v>
+        <v>15.62</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -957,8 +964,9 @@
         <v>0.95</v>
       </c>
       <c r="T6" t="n">
-        <v>5</v>
-      </c>
+        <v>14.84</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -968,82 +976,340 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Cuiaba x Athletic Club</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cuiaba</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M7" t="n">
+        <v>200</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8.039999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Criciuma x Juventude</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Over 4.5 FT</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>20</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="M8" t="n">
+        <v>100</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0x2</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>COLOMBIA 2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Internacional de Palmira x Atletico FC Cali</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Internacional de Palmira</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Atletico FC Cali</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Match Odds (Draw)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>LAY</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J9" t="n">
         <v>5.8</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K9" t="n">
         <v>1.36</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L9" t="n">
         <v>20.83</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M9" t="n">
         <v>100</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>0x1</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q9" t="n">
         <v>0.95</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="S9" t="n">
         <v>0.95</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T9" t="n">
         <v>19.79</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>COPA SUDAMERICANA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Boca Juniors x Sao Paulo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>24</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>200</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-08.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-08.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-08.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-08.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-08.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-08.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,19 +595,19 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -1028,19 +1028,19 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1287,19 +1287,19 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S10" t="n">
